--- a/src/hw/board_files/KuhnYork/BOM.xlsx
+++ b/src/hw/board_files/KuhnYork/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\gitRepos\golf-gps\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\gitRepos\golf-gps\src\hw\board_files\KuhnYork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FB8036-24B6-4115-8B42-5F18822F7FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E753D0BE-4E1B-4AA3-A0AA-9D75113E2149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BOM!$A$1:$H$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BOM!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="207">
-  <si>
-    <t>Quantity</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="209">
   <si>
     <t>Reference(s)</t>
   </si>
@@ -536,9 +533,6 @@
     <t>C7, C9, C11, C12, C15, C16, C19, C20</t>
   </si>
   <si>
-    <t>C10, 21</t>
-  </si>
-  <si>
     <t>C13, C14</t>
   </si>
   <si>
@@ -660,6 +654,31 @@
   </si>
   <si>
     <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>Qty.</t>
+  </si>
+  <si>
+    <t>C10, C21</t>
+  </si>
+  <si>
+    <t>MCP73871-1AAI/ML</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ETG Stock, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DNP R12, R13</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1075,7 +1094,7 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{32AFDCD7-F4DF-4ED5-8811-A4897B942137}" name="Quantity" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{32AFDCD7-F4DF-4ED5-8811-A4897B942137}" name="Qty." dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{FE933B93-DA18-4AED-A480-8EB2CB37E9FA}" name="Reference(s)" dataDxfId="7"/>
     <tableColumn id="10" xr3:uid="{F7578A95-5131-4E48-843B-E8DF71CB7A4C}" name="Description" dataDxfId="6"/>
     <tableColumn id="11" xr3:uid="{0E106ADB-04B7-4862-9B8C-0C8A8ACABA2E}" name="Package" dataDxfId="5"/>
@@ -1352,47 +1371,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
     <col min="3" max="3" width="37.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" customWidth="1"/>
+    <col min="7" max="7" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1400,24 +1422,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1425,24 +1447,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1450,23 +1472,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -1475,25 +1497,25 @@
         <v>7</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -1502,25 +1524,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="H6" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -1529,25 +1551,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="H7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -1556,22 +1578,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7"/>
@@ -1581,22 +1603,22 @@
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
@@ -1606,22 +1628,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
@@ -1631,25 +1653,25 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -1658,26 +1680,26 @@
         <v>1</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="F12" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,22 +1707,22 @@
         <v>1</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="7"/>
@@ -1710,24 +1732,24 @@
         <v>1</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1735,25 +1757,25 @@
         <v>1</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -1762,19 +1784,19 @@
         <v>1</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -1783,19 +1805,19 @@
         <v>1</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -1804,19 +1826,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -1825,24 +1847,24 @@
         <v>1</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1850,20 +1872,20 @@
         <v>1</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="7"/>
@@ -1873,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1881,7 +1903,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -1890,26 +1912,26 @@
         <v>1</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1917,26 +1939,26 @@
         <v>2</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1944,26 +1966,26 @@
         <v>1</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1971,25 +1993,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="H25" s="6" t="s">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="I25" s="7"/>
     </row>
@@ -1998,25 +2020,25 @@
         <v>5</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I26" s="7"/>
     </row>
@@ -2025,22 +2047,22 @@
         <v>2</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="7"/>
@@ -2050,25 +2072,25 @@
         <v>1</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="H28" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I28" s="7"/>
     </row>
@@ -2077,22 +2099,22 @@
         <v>1</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="F29" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="7"/>
@@ -2102,22 +2124,22 @@
         <v>2</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="7"/>
@@ -2127,23 +2149,23 @@
         <v>1</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="H31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I31" s="7"/>
     </row>
@@ -2152,17 +2174,17 @@
         <v>4</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I32" s="7"/>
     </row>
@@ -2171,26 +2193,26 @@
         <v>1</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2198,26 +2220,26 @@
         <v>1</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2225,26 +2247,26 @@
         <v>1</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F35" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2252,26 +2274,26 @@
         <v>1</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="E36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="G36" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2279,26 +2301,26 @@
         <v>1</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2306,26 +2328,26 @@
         <v>1</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2333,26 +2355,26 @@
         <v>1</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E39" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="G39" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2361,7 +2383,7 @@
         <v>73</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2375,7 +2397,7 @@
     <hyperlink ref="I37" r:id="rId4" xr:uid="{4295295F-C461-46B4-9FF8-784C0631F89D}"/>
   </hyperlinks>
   <pageMargins left="0.67965686274509796" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="59" orientation="landscape" r:id="rId5"/>
+  <pageSetup scale="64" fitToHeight="0" orientation="landscape" r:id="rId5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"-,Bold"&amp;14Golf GPS BOM&amp;RRev 1</oddHeader>
   </headerFooter>
